--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU07/HRM/pre LAM_HRM-2031-0480/Panel-28/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU07_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU07/HRM/pre LAM_HRM-2031-0480/Panel-28/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU07_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.42254</v>
+        <v>17.41421</v>
       </c>
       <c r="D2" t="n">
-        <v>16.80861</v>
+        <v>16.99433</v>
       </c>
       <c r="E2" t="n">
-        <v>17.15416</v>
+        <v>17.10035</v>
       </c>
       <c r="F2" t="n">
-        <v>43.2587</v>
+        <v>43.62099</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05194</v>
+        <v>0.05197</v>
       </c>
       <c r="H2" t="n">
-        <v>1.91988</v>
+        <v>1.88876</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.46301</v>
+        <v>17.33549</v>
       </c>
       <c r="D3" t="n">
-        <v>17.03687</v>
+        <v>16.77711</v>
       </c>
       <c r="E3" t="n">
-        <v>16.90369</v>
+        <v>17.2179</v>
       </c>
       <c r="F3" t="n">
-        <v>43.72436</v>
+        <v>43.0926</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05303</v>
+        <v>0.0516</v>
       </c>
       <c r="H3" t="n">
-        <v>1.93116</v>
+        <v>1.86735</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.96003</v>
+        <v>17.5493</v>
       </c>
       <c r="D4" t="n">
-        <v>16.99065</v>
+        <v>17.19701</v>
       </c>
       <c r="E4" t="n">
-        <v>17.15665</v>
+        <v>17.2065</v>
       </c>
       <c r="F4" t="n">
-        <v>43.12434</v>
+        <v>43.62635</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05219</v>
+        <v>0.05233</v>
       </c>
       <c r="H4" t="n">
-        <v>1.907</v>
+        <v>1.8647</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17.34876</v>
+        <v>17.34596</v>
       </c>
       <c r="D5" t="n">
-        <v>17.4249</v>
+        <v>17.0959</v>
       </c>
       <c r="E5" t="n">
-        <v>17.18551</v>
+        <v>17.22879</v>
       </c>
       <c r="F5" t="n">
-        <v>43.99665</v>
+        <v>44.15877</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05122</v>
+        <v>0.05244</v>
       </c>
       <c r="H5" t="n">
-        <v>1.86476</v>
+        <v>1.89773</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.80888</v>
+        <v>17.50149</v>
       </c>
       <c r="D6" t="n">
-        <v>17.17867</v>
+        <v>16.93522</v>
       </c>
       <c r="E6" t="n">
-        <v>17.36394</v>
+        <v>17.35215</v>
       </c>
       <c r="F6" t="n">
-        <v>43.2507</v>
+        <v>43.6978</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05258</v>
+        <v>0.05272</v>
       </c>
       <c r="H6" t="n">
-        <v>1.84041</v>
+        <v>1.86617</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.31513</v>
+        <v>17.29733</v>
       </c>
       <c r="D7" t="n">
-        <v>17.27357</v>
+        <v>17.02682</v>
       </c>
       <c r="E7" t="n">
-        <v>17.08031</v>
+        <v>17.13781</v>
       </c>
       <c r="F7" t="n">
-        <v>43.95618</v>
+        <v>43.55799</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05171</v>
+        <v>0.05343</v>
       </c>
       <c r="H7" t="n">
-        <v>1.93436</v>
+        <v>1.90339</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.36323</v>
+        <v>17.14832</v>
       </c>
       <c r="D8" t="n">
-        <v>17.32546</v>
+        <v>17.01622</v>
       </c>
       <c r="E8" t="n">
-        <v>17.10609</v>
+        <v>17.1042</v>
       </c>
       <c r="F8" t="n">
-        <v>43.3937</v>
+        <v>43.87846</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05193</v>
+        <v>0.05212</v>
       </c>
       <c r="H8" t="n">
-        <v>1.85199</v>
+        <v>1.84626</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17.51118</v>
+        <v>17.56724</v>
       </c>
       <c r="D9" t="n">
-        <v>17.052</v>
+        <v>16.77461</v>
       </c>
       <c r="E9" t="n">
-        <v>17.36631</v>
+        <v>17.0449</v>
       </c>
       <c r="F9" t="n">
-        <v>43.61012</v>
+        <v>44.74927</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0512</v>
+        <v>0.05237</v>
       </c>
       <c r="H9" t="n">
-        <v>1.86429</v>
+        <v>1.90361</v>
       </c>
     </row>
     <row r="10">
@@ -660,22 +660,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17.15124</v>
+        <v>17.48392</v>
       </c>
       <c r="D10" t="n">
-        <v>17.07861</v>
+        <v>16.94249</v>
       </c>
       <c r="E10" t="n">
-        <v>17.14442</v>
+        <v>17.19241</v>
       </c>
       <c r="F10" t="n">
-        <v>42.66598</v>
+        <v>44.15793</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05204</v>
+        <v>0.05302</v>
       </c>
       <c r="H10" t="n">
-        <v>1.88068</v>
+        <v>1.89412</v>
       </c>
     </row>
     <row r="11">
@@ -722,22 +722,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.91191</v>
+        <v>17.23829</v>
       </c>
       <c r="D12" t="n">
-        <v>16.91035</v>
+        <v>16.83052</v>
       </c>
       <c r="E12" t="n">
-        <v>17.4155</v>
+        <v>17.08618</v>
       </c>
       <c r="F12" t="n">
-        <v>44.91422</v>
+        <v>43.1446</v>
       </c>
       <c r="G12" t="n">
-        <v>0.05082</v>
+        <v>0.05348</v>
       </c>
       <c r="H12" t="n">
-        <v>1.88614</v>
+        <v>1.88693</v>
       </c>
     </row>
     <row r="13">
@@ -747,22 +747,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>17.47165</v>
+        <v>17.26595</v>
       </c>
       <c r="D13" t="n">
-        <v>16.80985</v>
+        <v>16.99782</v>
       </c>
       <c r="E13" t="n">
-        <v>16.908</v>
+        <v>17.22809</v>
       </c>
       <c r="F13" t="n">
-        <v>43.02689</v>
+        <v>43.00593</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0513</v>
+        <v>0.05321</v>
       </c>
       <c r="H13" t="n">
-        <v>1.88829</v>
+        <v>1.90534</v>
       </c>
     </row>
     <row r="14">
@@ -772,22 +772,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>17.31902</v>
+        <v>17.38001</v>
       </c>
       <c r="D14" t="n">
-        <v>17.1628</v>
+        <v>17.03408</v>
       </c>
       <c r="E14" t="n">
-        <v>16.76931</v>
+        <v>17.06974</v>
       </c>
       <c r="F14" t="n">
-        <v>44.01043</v>
+        <v>43.92733</v>
       </c>
       <c r="G14" t="n">
-        <v>0.05083</v>
+        <v>0.05094</v>
       </c>
       <c r="H14" t="n">
-        <v>1.84943</v>
+        <v>1.87677</v>
       </c>
     </row>
     <row r="15">
@@ -797,22 +797,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>17.45392</v>
+        <v>17.27233</v>
       </c>
       <c r="D15" t="n">
-        <v>17.18482</v>
+        <v>17.22024</v>
       </c>
       <c r="E15" t="n">
-        <v>17.11942</v>
+        <v>17.24802</v>
       </c>
       <c r="F15" t="n">
-        <v>43.708</v>
+        <v>43.99201</v>
       </c>
       <c r="G15" t="n">
-        <v>0.05283</v>
+        <v>0.05172</v>
       </c>
       <c r="H15" t="n">
-        <v>1.88638</v>
+        <v>1.90554</v>
       </c>
     </row>
     <row r="16">
@@ -822,22 +822,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>17.77807</v>
+        <v>17.19052</v>
       </c>
       <c r="D16" t="n">
-        <v>17.12241</v>
+        <v>17.04611</v>
       </c>
       <c r="E16" t="n">
-        <v>16.82078</v>
+        <v>17.0911</v>
       </c>
       <c r="F16" t="n">
-        <v>43.14376</v>
+        <v>42.77678</v>
       </c>
       <c r="G16" t="n">
-        <v>0.05294</v>
+        <v>0.05293</v>
       </c>
       <c r="H16" t="n">
-        <v>1.86852</v>
+        <v>1.88618</v>
       </c>
     </row>
     <row r="17">
@@ -847,22 +847,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16.99729</v>
+        <v>17.33313</v>
       </c>
       <c r="D17" t="n">
-        <v>16.8635</v>
+        <v>16.63769</v>
       </c>
       <c r="E17" t="n">
-        <v>17.34807</v>
+        <v>17.20617</v>
       </c>
       <c r="F17" t="n">
-        <v>44.17255</v>
+        <v>44.72762</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0519</v>
+        <v>0.05258</v>
       </c>
       <c r="H17" t="n">
-        <v>1.89545</v>
+        <v>1.92672</v>
       </c>
     </row>
     <row r="18">
@@ -872,22 +872,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16.90983</v>
+        <v>17.44167</v>
       </c>
       <c r="D18" t="n">
-        <v>16.79873</v>
+        <v>17.01052</v>
       </c>
       <c r="E18" t="n">
-        <v>16.97288</v>
+        <v>17.39224</v>
       </c>
       <c r="F18" t="n">
-        <v>43.8136</v>
+        <v>44.00977</v>
       </c>
       <c r="G18" t="n">
-        <v>0.05311</v>
+        <v>0.05217</v>
       </c>
       <c r="H18" t="n">
-        <v>1.85457</v>
+        <v>1.89856</v>
       </c>
     </row>
     <row r="19">
@@ -897,22 +897,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>17.20005</v>
+        <v>17.72881</v>
       </c>
       <c r="D19" t="n">
-        <v>17.48388</v>
+        <v>17.23027</v>
       </c>
       <c r="E19" t="n">
-        <v>17.10943</v>
+        <v>17.2332</v>
       </c>
       <c r="F19" t="n">
-        <v>44.37827</v>
+        <v>44.00595</v>
       </c>
       <c r="G19" t="n">
-        <v>0.05233</v>
+        <v>0.05234</v>
       </c>
       <c r="H19" t="n">
-        <v>1.88319</v>
+        <v>1.89767</v>
       </c>
     </row>
     <row r="20">
@@ -922,22 +922,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>17.30837</v>
+        <v>17.23797</v>
       </c>
       <c r="D20" t="n">
-        <v>16.65404</v>
+        <v>16.96356</v>
       </c>
       <c r="E20" t="n">
-        <v>17.19907</v>
+        <v>17.04633</v>
       </c>
       <c r="F20" t="n">
-        <v>43.39699</v>
+        <v>42.86446</v>
       </c>
       <c r="G20" t="n">
-        <v>0.05263</v>
+        <v>0.05181</v>
       </c>
       <c r="H20" t="n">
-        <v>1.85421</v>
+        <v>1.86601</v>
       </c>
     </row>
     <row r="21">
@@ -974,16 +974,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>16.43926</v>
+        <v>16.18169</v>
       </c>
       <c r="D22" t="n">
-        <v>15.96911</v>
+        <v>15.81113</v>
       </c>
       <c r="E22" t="n">
-        <v>16.19409</v>
+        <v>16.08503</v>
       </c>
       <c r="F22" t="n">
-        <v>269.18299</v>
+        <v>261.04207</v>
       </c>
     </row>
     <row r="23">
@@ -993,16 +993,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>16.25241</v>
+        <v>16.23335</v>
       </c>
       <c r="D23" t="n">
-        <v>15.9809</v>
+        <v>15.97993</v>
       </c>
       <c r="E23" t="n">
-        <v>15.95983</v>
+        <v>16.13634</v>
       </c>
       <c r="F23" t="n">
-        <v>262.07707</v>
+        <v>258.08133</v>
       </c>
     </row>
     <row r="24">
@@ -1012,16 +1012,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>15.81865</v>
+        <v>16.19998</v>
       </c>
       <c r="D24" t="n">
-        <v>16.08631</v>
+        <v>15.83521</v>
       </c>
       <c r="E24" t="n">
-        <v>15.84103</v>
+        <v>16.05008</v>
       </c>
       <c r="F24" t="n">
-        <v>264.66255</v>
+        <v>268.88722</v>
       </c>
     </row>
     <row r="25">
@@ -1031,16 +1031,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>16.11014</v>
+        <v>16.21724</v>
       </c>
       <c r="D25" t="n">
-        <v>15.92424</v>
+        <v>15.62052</v>
       </c>
       <c r="E25" t="n">
-        <v>16.03321</v>
+        <v>15.74155</v>
       </c>
       <c r="F25" t="n">
-        <v>260.50256</v>
+        <v>255.93749</v>
       </c>
     </row>
     <row r="26">
@@ -1050,16 +1050,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>16.37927</v>
+        <v>16.46604</v>
       </c>
       <c r="D26" t="n">
-        <v>16.03466</v>
+        <v>16.16891</v>
       </c>
       <c r="E26" t="n">
-        <v>16.28183</v>
+        <v>16.33723</v>
       </c>
       <c r="F26" t="n">
-        <v>264.74259</v>
+        <v>265.27852</v>
       </c>
     </row>
     <row r="27">
@@ -1069,16 +1069,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>16.15001</v>
+        <v>16.33485</v>
       </c>
       <c r="D27" t="n">
-        <v>16.0473</v>
+        <v>16.05928</v>
       </c>
       <c r="E27" t="n">
-        <v>16.37902</v>
+        <v>16.07385</v>
       </c>
       <c r="F27" t="n">
-        <v>262.36282</v>
+        <v>263.55989</v>
       </c>
     </row>
     <row r="28">
@@ -1088,16 +1088,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>15.91541</v>
+        <v>16.19334</v>
       </c>
       <c r="D28" t="n">
-        <v>16.10654</v>
+        <v>16.01316</v>
       </c>
       <c r="E28" t="n">
-        <v>16.30751</v>
+        <v>16.03799</v>
       </c>
       <c r="F28" t="n">
-        <v>253.66899</v>
+        <v>266.01282</v>
       </c>
     </row>
     <row r="29">
@@ -1107,16 +1107,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>16.16776</v>
+        <v>16.22677</v>
       </c>
       <c r="D29" t="n">
-        <v>15.98479</v>
+        <v>15.78939</v>
       </c>
       <c r="E29" t="n">
-        <v>16.25484</v>
+        <v>15.96611</v>
       </c>
       <c r="F29" t="n">
-        <v>259.61416</v>
+        <v>261.57661</v>
       </c>
     </row>
     <row r="30">
@@ -1126,16 +1126,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>15.97513</v>
+        <v>16.06339</v>
       </c>
       <c r="D30" t="n">
-        <v>16.23637</v>
+        <v>15.82133</v>
       </c>
       <c r="E30" t="n">
-        <v>16.08605</v>
+        <v>15.91123</v>
       </c>
       <c r="F30" t="n">
-        <v>261.09044</v>
+        <v>262.35257</v>
       </c>
     </row>
     <row r="31">
@@ -1177,19 +1177,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>17.41263</v>
+        <v>17.72249</v>
       </c>
       <c r="D32" t="n">
-        <v>16.56007</v>
+        <v>16.36773</v>
       </c>
       <c r="E32" t="n">
-        <v>16.87714</v>
+        <v>16.84889</v>
       </c>
       <c r="F32" t="n">
-        <v>22.22298</v>
+        <v>22.61725</v>
       </c>
       <c r="G32" t="n">
-        <v>35.96536</v>
+        <v>34.91772</v>
       </c>
     </row>
     <row r="33">
@@ -1199,19 +1199,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>17.26017</v>
+        <v>17.55262</v>
       </c>
       <c r="D33" t="n">
-        <v>16.57756</v>
+        <v>16.23568</v>
       </c>
       <c r="E33" t="n">
-        <v>17.0797</v>
+        <v>16.78612</v>
       </c>
       <c r="F33" t="n">
-        <v>22.29176</v>
+        <v>22.3474</v>
       </c>
       <c r="G33" t="n">
-        <v>34.45407</v>
+        <v>34.03057</v>
       </c>
     </row>
     <row r="34">
@@ -1221,19 +1221,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>17.57441</v>
+        <v>17.08213</v>
       </c>
       <c r="D34" t="n">
-        <v>16.74252</v>
+        <v>16.63075</v>
       </c>
       <c r="E34" t="n">
-        <v>16.75978</v>
+        <v>16.75586</v>
       </c>
       <c r="F34" t="n">
-        <v>22.23664</v>
+        <v>22.71152</v>
       </c>
       <c r="G34" t="n">
-        <v>35.28454</v>
+        <v>35.11326</v>
       </c>
     </row>
     <row r="35">
@@ -1243,19 +1243,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>16.75782</v>
+        <v>17.26188</v>
       </c>
       <c r="D35" t="n">
-        <v>16.32086</v>
+        <v>16.28829</v>
       </c>
       <c r="E35" t="n">
-        <v>17.07455</v>
+        <v>16.84414</v>
       </c>
       <c r="F35" t="n">
-        <v>22.46101</v>
+        <v>22.29025</v>
       </c>
       <c r="G35" t="n">
-        <v>35.15024</v>
+        <v>35.09</v>
       </c>
     </row>
     <row r="36">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>17.02217</v>
+        <v>17.08841</v>
       </c>
       <c r="D36" t="n">
-        <v>16.41849</v>
+        <v>16.46712</v>
       </c>
       <c r="E36" t="n">
-        <v>16.52988</v>
+        <v>16.64917</v>
       </c>
       <c r="F36" t="n">
-        <v>22.32449</v>
+        <v>22.76214</v>
       </c>
       <c r="G36" t="n">
-        <v>35.35731</v>
+        <v>35.66039</v>
       </c>
     </row>
     <row r="37">
@@ -1287,19 +1287,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>17.23073</v>
+        <v>17.33728</v>
       </c>
       <c r="D37" t="n">
-        <v>16.16853</v>
+        <v>16.38747</v>
       </c>
       <c r="E37" t="n">
-        <v>17.01723</v>
+        <v>16.95505</v>
       </c>
       <c r="F37" t="n">
-        <v>22.35106</v>
+        <v>22.60539</v>
       </c>
       <c r="G37" t="n">
-        <v>34.99319</v>
+        <v>34.7671</v>
       </c>
     </row>
     <row r="38">
@@ -1309,19 +1309,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>17.20792</v>
+        <v>16.92949</v>
       </c>
       <c r="D38" t="n">
-        <v>16.19107</v>
+        <v>16.66156</v>
       </c>
       <c r="E38" t="n">
-        <v>17.03833</v>
+        <v>16.79777</v>
       </c>
       <c r="F38" t="n">
-        <v>22.30766</v>
+        <v>22.6652</v>
       </c>
       <c r="G38" t="n">
-        <v>35.63645</v>
+        <v>35.51604</v>
       </c>
     </row>
     <row r="39">
@@ -1331,19 +1331,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>16.56665</v>
+        <v>17.45604</v>
       </c>
       <c r="D39" t="n">
-        <v>16.52221</v>
+        <v>15.93321</v>
       </c>
       <c r="E39" t="n">
-        <v>17.11424</v>
+        <v>16.66217</v>
       </c>
       <c r="F39" t="n">
-        <v>22.44857</v>
+        <v>23.00526</v>
       </c>
       <c r="G39" t="n">
-        <v>35.17074</v>
+        <v>35.50007</v>
       </c>
     </row>
     <row r="40">
@@ -1353,19 +1353,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>16.82015</v>
+        <v>16.93545</v>
       </c>
       <c r="D40" t="n">
-        <v>16.57333</v>
+        <v>16.51129</v>
       </c>
       <c r="E40" t="n">
-        <v>16.99047</v>
+        <v>16.58145</v>
       </c>
       <c r="F40" t="n">
-        <v>22.98413</v>
+        <v>22.31339</v>
       </c>
       <c r="G40" t="n">
-        <v>35.70068</v>
+        <v>35.76017</v>
       </c>
     </row>
     <row r="41">
@@ -1407,19 +1407,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>17.07407</v>
+        <v>16.9755</v>
       </c>
       <c r="D42" t="n">
-        <v>16.4386</v>
+        <v>16.16233</v>
       </c>
       <c r="E42" t="n">
-        <v>16.74496</v>
+        <v>16.87385</v>
       </c>
       <c r="F42" t="n">
-        <v>22.02964</v>
+        <v>21.96147</v>
       </c>
       <c r="G42" t="n">
-        <v>34.84066</v>
+        <v>35.32708</v>
       </c>
     </row>
     <row r="43">
@@ -1429,19 +1429,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>17.3409</v>
+        <v>17.20194</v>
       </c>
       <c r="D43" t="n">
-        <v>16.31786</v>
+        <v>16.53008</v>
       </c>
       <c r="E43" t="n">
-        <v>16.50951</v>
+        <v>17.10727</v>
       </c>
       <c r="F43" t="n">
-        <v>22.19365</v>
+        <v>22.41006</v>
       </c>
       <c r="G43" t="n">
-        <v>35.05753</v>
+        <v>34.76237</v>
       </c>
     </row>
     <row r="44">
@@ -1451,19 +1451,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>17.24062</v>
+        <v>17.10047</v>
       </c>
       <c r="D44" t="n">
-        <v>16.70363</v>
+        <v>16.19411</v>
       </c>
       <c r="E44" t="n">
-        <v>17.21342</v>
+        <v>16.64003</v>
       </c>
       <c r="F44" t="n">
-        <v>22.08818</v>
+        <v>22.24989</v>
       </c>
       <c r="G44" t="n">
-        <v>35.17139</v>
+        <v>35.66197</v>
       </c>
     </row>
     <row r="45">
@@ -1473,19 +1473,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>17.24851</v>
+        <v>17.28263</v>
       </c>
       <c r="D45" t="n">
-        <v>16.67227</v>
+        <v>16.35683</v>
       </c>
       <c r="E45" t="n">
-        <v>16.88557</v>
+        <v>17.27781</v>
       </c>
       <c r="F45" t="n">
-        <v>22.22995</v>
+        <v>22.67833</v>
       </c>
       <c r="G45" t="n">
-        <v>35.10955</v>
+        <v>34.78592</v>
       </c>
     </row>
     <row r="46">
@@ -1495,19 +1495,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>17.40806</v>
+        <v>17.09785</v>
       </c>
       <c r="D46" t="n">
-        <v>16.67057</v>
+        <v>16.57205</v>
       </c>
       <c r="E46" t="n">
-        <v>17.03055</v>
+        <v>17.04143</v>
       </c>
       <c r="F46" t="n">
-        <v>22.33409</v>
+        <v>22.25267</v>
       </c>
       <c r="G46" t="n">
-        <v>35.27553</v>
+        <v>34.92747</v>
       </c>
     </row>
     <row r="47">
@@ -1517,19 +1517,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>16.91977</v>
+        <v>16.90749</v>
       </c>
       <c r="D47" t="n">
-        <v>16.53162</v>
+        <v>16.30495</v>
       </c>
       <c r="E47" t="n">
-        <v>17.11872</v>
+        <v>16.68582</v>
       </c>
       <c r="F47" t="n">
-        <v>22.75895</v>
+        <v>22.65</v>
       </c>
       <c r="G47" t="n">
-        <v>35.25637</v>
+        <v>34.40883</v>
       </c>
     </row>
     <row r="48">
@@ -1539,19 +1539,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>17.35558</v>
+        <v>17.59362</v>
       </c>
       <c r="D48" t="n">
-        <v>16.52121</v>
+        <v>16.32627</v>
       </c>
       <c r="E48" t="n">
-        <v>17.04596</v>
+        <v>17.0661</v>
       </c>
       <c r="F48" t="n">
-        <v>22.07823</v>
+        <v>22.48449</v>
       </c>
       <c r="G48" t="n">
-        <v>35.529</v>
+        <v>34.90748</v>
       </c>
     </row>
     <row r="49">
@@ -1561,19 +1561,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>17.10408</v>
+        <v>17.48574</v>
       </c>
       <c r="D49" t="n">
-        <v>16.48457</v>
+        <v>16.42982</v>
       </c>
       <c r="E49" t="n">
-        <v>17.07874</v>
+        <v>16.94353</v>
       </c>
       <c r="F49" t="n">
-        <v>22.53479</v>
+        <v>22.74017</v>
       </c>
       <c r="G49" t="n">
-        <v>35.10663</v>
+        <v>35.52221</v>
       </c>
     </row>
     <row r="50">
@@ -1583,19 +1583,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>17.33837</v>
+        <v>17.31837</v>
       </c>
       <c r="D50" t="n">
-        <v>16.65392</v>
+        <v>16.17537</v>
       </c>
       <c r="E50" t="n">
-        <v>16.71296</v>
+        <v>16.83543</v>
       </c>
       <c r="F50" t="n">
-        <v>22.10766</v>
+        <v>22.124</v>
       </c>
       <c r="G50" t="n">
-        <v>35.06544</v>
+        <v>35.85259</v>
       </c>
     </row>
     <row r="51">
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.62723</v>
+        <v>0.63174</v>
       </c>
       <c r="D52" t="n">
-        <v>1.14863</v>
+        <v>1.16614</v>
       </c>
     </row>
     <row r="53">
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0.63012</v>
+        <v>0.62058</v>
       </c>
       <c r="D53" t="n">
-        <v>1.14881</v>
+        <v>1.16072</v>
       </c>
     </row>
     <row r="54">
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0.62781</v>
+        <v>0.6241100000000001</v>
       </c>
       <c r="D54" t="n">
-        <v>1.15184</v>
+        <v>1.14755</v>
       </c>
     </row>
     <row r="55">
@@ -1661,10 +1661,10 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0.62942</v>
+        <v>0.61971</v>
       </c>
       <c r="D55" t="n">
-        <v>1.13772</v>
+        <v>1.14003</v>
       </c>
     </row>
     <row r="56">
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>0.61878</v>
+        <v>0.62232</v>
       </c>
       <c r="D56" t="n">
-        <v>1.15</v>
+        <v>1.1408</v>
       </c>
     </row>
     <row r="57">
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0.6273300000000001</v>
+        <v>0.63376</v>
       </c>
       <c r="D57" t="n">
-        <v>1.11227</v>
+        <v>1.15168</v>
       </c>
     </row>
     <row r="58">
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>0.62331</v>
+        <v>0.6137899999999999</v>
       </c>
       <c r="D58" t="n">
-        <v>1.15708</v>
+        <v>1.11912</v>
       </c>
     </row>
     <row r="59">
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0.6198</v>
+        <v>0.62876</v>
       </c>
       <c r="D59" t="n">
-        <v>1.1533</v>
+        <v>1.15507</v>
       </c>
     </row>
     <row r="60">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.62486</v>
+        <v>0.61664</v>
       </c>
       <c r="D60" t="n">
-        <v>1.15433</v>
+        <v>1.14174</v>
       </c>
     </row>
     <row r="61">
@@ -1756,10 +1756,10 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>0.62364</v>
+        <v>0.63159</v>
       </c>
       <c r="D62" t="n">
-        <v>1.15654</v>
+        <v>1.16086</v>
       </c>
     </row>
     <row r="63">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>0.62507</v>
+        <v>0.61433</v>
       </c>
       <c r="D63" t="n">
-        <v>1.13923</v>
+        <v>1.14614</v>
       </c>
     </row>
     <row r="64">
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>0.62629</v>
+        <v>0.61926</v>
       </c>
       <c r="D64" t="n">
-        <v>1.15814</v>
+        <v>1.15576</v>
       </c>
     </row>
     <row r="65">
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>0.6277700000000001</v>
+        <v>0.62757</v>
       </c>
       <c r="D65" t="n">
-        <v>1.14879</v>
+        <v>1.14151</v>
       </c>
     </row>
     <row r="66">
@@ -1808,10 +1808,10 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>0.61419</v>
+        <v>0.63063</v>
       </c>
       <c r="D66" t="n">
-        <v>1.13924</v>
+        <v>1.15899</v>
       </c>
     </row>
     <row r="67">
@@ -1821,10 +1821,10 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>0.60273</v>
+        <v>0.63642</v>
       </c>
       <c r="D67" t="n">
-        <v>1.15245</v>
+        <v>1.14236</v>
       </c>
     </row>
     <row r="68">
@@ -1834,10 +1834,10 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>0.62943</v>
+        <v>0.61682</v>
       </c>
       <c r="D68" t="n">
-        <v>1.12851</v>
+        <v>1.15625</v>
       </c>
     </row>
     <row r="69">
@@ -1847,10 +1847,10 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>0.6359900000000001</v>
+        <v>0.62837</v>
       </c>
       <c r="D69" t="n">
-        <v>1.1497</v>
+        <v>1.15474</v>
       </c>
     </row>
     <row r="70">
@@ -1860,10 +1860,10 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>0.62896</v>
+        <v>0.6373799999999999</v>
       </c>
       <c r="D70" t="n">
-        <v>1.13883</v>
+        <v>1.13459</v>
       </c>
     </row>
     <row r="71">
@@ -1920,28 +1920,28 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>0.77105</v>
+        <v>0.77717</v>
       </c>
       <c r="D72" t="n">
-        <v>0.08411</v>
+        <v>0.08561000000000001</v>
       </c>
       <c r="E72" t="n">
-        <v>0.62425</v>
+        <v>0.62822</v>
       </c>
       <c r="F72" t="n">
-        <v>0.98059</v>
+        <v>0.99199</v>
       </c>
       <c r="G72" t="n">
-        <v>0.11336</v>
+        <v>0.1107</v>
       </c>
       <c r="H72" t="n">
-        <v>0.00783</v>
+        <v>0.00779</v>
       </c>
       <c r="I72" t="n">
-        <v>0.09709</v>
+        <v>0.09611</v>
       </c>
       <c r="J72" t="n">
-        <v>0.12915</v>
+        <v>0.13089</v>
       </c>
     </row>
     <row r="73">
@@ -1951,28 +1951,28 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>0.75958</v>
+        <v>0.77786</v>
       </c>
       <c r="D73" t="n">
-        <v>0.083</v>
+        <v>0.08338</v>
       </c>
       <c r="E73" t="n">
-        <v>0.6257200000000001</v>
+        <v>0.61466</v>
       </c>
       <c r="F73" t="n">
-        <v>0.98036</v>
+        <v>0.95438</v>
       </c>
       <c r="G73" t="n">
-        <v>0.11298</v>
+        <v>0.11311</v>
       </c>
       <c r="H73" t="n">
-        <v>0.00772</v>
+        <v>0.00791</v>
       </c>
       <c r="I73" t="n">
-        <v>0.09608999999999999</v>
+        <v>0.09538000000000001</v>
       </c>
       <c r="J73" t="n">
-        <v>0.13254</v>
+        <v>0.13031</v>
       </c>
     </row>
     <row r="74">
@@ -1982,28 +1982,28 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>0.77171</v>
+        <v>0.77785</v>
       </c>
       <c r="D74" t="n">
-        <v>0.08389000000000001</v>
+        <v>0.08348999999999999</v>
       </c>
       <c r="E74" t="n">
-        <v>0.6211100000000001</v>
+        <v>0.61605</v>
       </c>
       <c r="F74" t="n">
-        <v>0.98506</v>
+        <v>0.99279</v>
       </c>
       <c r="G74" t="n">
-        <v>0.1115</v>
+        <v>0.11165</v>
       </c>
       <c r="H74" t="n">
-        <v>0.00784</v>
+        <v>0.00795</v>
       </c>
       <c r="I74" t="n">
-        <v>0.09535</v>
+        <v>0.09621</v>
       </c>
       <c r="J74" t="n">
-        <v>0.12816</v>
+        <v>0.12893</v>
       </c>
     </row>
     <row r="75">
@@ -2013,28 +2013,28 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>0.76231</v>
+        <v>0.78539</v>
       </c>
       <c r="D75" t="n">
-        <v>0.08279</v>
+        <v>0.08452</v>
       </c>
       <c r="E75" t="n">
-        <v>0.63305</v>
+        <v>0.63427</v>
       </c>
       <c r="F75" t="n">
-        <v>0.99249</v>
+        <v>0.99063</v>
       </c>
       <c r="G75" t="n">
-        <v>0.11366</v>
+        <v>0.11299</v>
       </c>
       <c r="H75" t="n">
-        <v>0.007860000000000001</v>
+        <v>0.007820000000000001</v>
       </c>
       <c r="I75" t="n">
-        <v>0.09369</v>
+        <v>0.09714</v>
       </c>
       <c r="J75" t="n">
-        <v>0.12921</v>
+        <v>0.13114</v>
       </c>
     </row>
     <row r="76">
@@ -2044,28 +2044,28 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>0.77197</v>
+        <v>0.77281</v>
       </c>
       <c r="D76" t="n">
-        <v>0.08461</v>
+        <v>0.08263</v>
       </c>
       <c r="E76" t="n">
-        <v>0.61812</v>
+        <v>0.63378</v>
       </c>
       <c r="F76" t="n">
-        <v>0.98581</v>
+        <v>0.98073</v>
       </c>
       <c r="G76" t="n">
-        <v>0.11483</v>
+        <v>0.11184</v>
       </c>
       <c r="H76" t="n">
-        <v>0.00793</v>
+        <v>0.007860000000000001</v>
       </c>
       <c r="I76" t="n">
-        <v>0.09512</v>
+        <v>0.09411</v>
       </c>
       <c r="J76" t="n">
-        <v>0.12932</v>
+        <v>0.12891</v>
       </c>
     </row>
     <row r="77">
@@ -2075,28 +2075,28 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>0.7763</v>
+        <v>0.78135</v>
       </c>
       <c r="D77" t="n">
-        <v>0.08395</v>
+        <v>0.08239</v>
       </c>
       <c r="E77" t="n">
-        <v>0.62764</v>
+        <v>0.62161</v>
       </c>
       <c r="F77" t="n">
-        <v>0.99077</v>
+        <v>0.98792</v>
       </c>
       <c r="G77" t="n">
-        <v>0.11187</v>
+        <v>0.11135</v>
       </c>
       <c r="H77" t="n">
-        <v>0.00795</v>
+        <v>0.007860000000000001</v>
       </c>
       <c r="I77" t="n">
-        <v>0.09707</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="J77" t="n">
-        <v>0.12939</v>
+        <v>0.13014</v>
       </c>
     </row>
     <row r="78">
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>0.7764799999999999</v>
+        <v>0.76445</v>
       </c>
       <c r="D78" t="n">
-        <v>0.08295</v>
+        <v>0.08298999999999999</v>
       </c>
       <c r="E78" t="n">
-        <v>0.63006</v>
+        <v>0.63004</v>
       </c>
       <c r="F78" t="n">
-        <v>0.9972</v>
+        <v>0.97889</v>
       </c>
       <c r="G78" t="n">
-        <v>0.11268</v>
+        <v>0.11463</v>
       </c>
       <c r="H78" t="n">
-        <v>0.00801</v>
+        <v>0.007860000000000001</v>
       </c>
       <c r="I78" t="n">
-        <v>0.09427000000000001</v>
+        <v>0.09597</v>
       </c>
       <c r="J78" t="n">
-        <v>0.13129</v>
+        <v>0.13078</v>
       </c>
     </row>
     <row r="79">
@@ -2137,28 +2137,28 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>0.77241</v>
+        <v>0.75917</v>
       </c>
       <c r="D79" t="n">
-        <v>0.08255999999999999</v>
+        <v>0.08351</v>
       </c>
       <c r="E79" t="n">
-        <v>0.62214</v>
+        <v>0.63402</v>
       </c>
       <c r="F79" t="n">
-        <v>0.98947</v>
+        <v>0.98637</v>
       </c>
       <c r="G79" t="n">
-        <v>0.11321</v>
+        <v>0.11307</v>
       </c>
       <c r="H79" t="n">
-        <v>0.007849999999999999</v>
+        <v>0.007820000000000001</v>
       </c>
       <c r="I79" t="n">
-        <v>0.09496</v>
+        <v>0.09626999999999999</v>
       </c>
       <c r="J79" t="n">
-        <v>0.13068</v>
+        <v>0.13155</v>
       </c>
     </row>
     <row r="80">
@@ -2168,28 +2168,28 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>0.75923</v>
+        <v>0.76309</v>
       </c>
       <c r="D80" t="n">
-        <v>0.08271000000000001</v>
+        <v>0.08198</v>
       </c>
       <c r="E80" t="n">
-        <v>0.63219</v>
+        <v>0.62846</v>
       </c>
       <c r="F80" t="n">
-        <v>0.9945000000000001</v>
+        <v>0.99587</v>
       </c>
       <c r="G80" t="n">
-        <v>0.11307</v>
+        <v>0.1101</v>
       </c>
       <c r="H80" t="n">
-        <v>0.007849999999999999</v>
+        <v>0.0078</v>
       </c>
       <c r="I80" t="n">
-        <v>0.09636</v>
+        <v>0.09486</v>
       </c>
       <c r="J80" t="n">
-        <v>0.13141</v>
+        <v>0.12999</v>
       </c>
     </row>
   </sheetData>
